--- a/megacem-react/server/templates/GMC-Holcim.Template.xlsx
+++ b/megacem-react/server/templates/GMC-Holcim.Template.xlsx
@@ -1,29 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M2EncoderEarl\BILLING\GMC Billing\Holcim\2025\December\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M2EncoderEarl\Github\megacem-web\megacem-react\server\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC854BD-333E-454C-AFBD-EE93E9968A0A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89203BE8-6652-49C3-934D-ACBCD9972256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="GMC HOLCIM BILLING" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'GMC HOLCIM BILLING'!$B$17:$L$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$B$17:$L$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
   <si>
     <t>Billing Statement</t>
   </si>
@@ -104,12 +118,6 @@
     <t>Driver's report</t>
   </si>
   <si>
-    <t>GREEN MEGACYCLE - HOLCIM PLANT</t>
-  </si>
-  <si>
-    <t>DUMPTRAILER</t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
@@ -162,12 +170,6 @@
   </si>
   <si>
     <t>618-117-819-0000</t>
-  </si>
-  <si>
-    <t>MTI DR - 00093101</t>
-  </si>
-  <si>
-    <t>MTI DR - 00093102</t>
   </si>
   <si>
     <t>December 5, 2025</t>
@@ -301,7 +303,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -324,6 +326,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFEEECE1"/>
       </patternFill>
     </fill>
   </fills>
@@ -615,7 +629,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -638,9 +652,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -668,9 +679,6 @@
     <xf numFmtId="4" fontId="2" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -681,26 +689,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -716,40 +709,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -761,16 +727,9 @@
     <xf numFmtId="4" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -823,16 +782,83 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -842,22 +868,14 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1165,18 +1183,18 @@
     </row>
     <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="22"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="28" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="30"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="72"/>
       <c r="L2" s="5"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
@@ -1196,16 +1214,16 @@
     </row>
     <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="24"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="22"/>
       <c r="L3" s="5"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -1225,16 +1243,16 @@
     </row>
     <row r="4" spans="1:27" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="33"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="76"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="25"/>
       <c r="L4" s="5"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -1254,20 +1272,20 @@
     </row>
     <row r="5" spans="1:27" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="43" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="89">
         <v>46004</v>
       </c>
-      <c r="J5" s="45"/>
-      <c r="K5" s="46"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="91"/>
       <c r="L5" s="7"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
@@ -1287,18 +1305,18 @@
     </row>
     <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="50" t="s">
+      <c r="B6" s="33"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="I6" s="51"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="53"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="93"/>
+      <c r="K6" s="94"/>
       <c r="L6" s="5"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
@@ -1318,22 +1336,22 @@
     </row>
     <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="50" t="s">
+      <c r="C7" s="71"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="84"/>
+      <c r="H7" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="I7" s="55" t="s">
-        <v>47</v>
+      <c r="I7" s="73" t="s">
+        <v>43</v>
       </c>
-      <c r="J7" s="29"/>
-      <c r="K7" s="30"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="72"/>
       <c r="L7" s="5"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -1353,20 +1371,20 @@
     </row>
     <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
-      <c r="B8" s="56" t="s">
+      <c r="B8" s="95" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="57"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="50" t="s">
+      <c r="C8" s="78"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="84"/>
+      <c r="H8" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="I8" s="55"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="30"/>
+      <c r="I8" s="73"/>
+      <c r="J8" s="71"/>
+      <c r="K8" s="72"/>
       <c r="L8" s="5"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
@@ -1386,18 +1404,18 @@
     </row>
     <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
-      <c r="B9" s="59" t="s">
-        <v>41</v>
+      <c r="B9" s="96" t="s">
+        <v>39</v>
       </c>
-      <c r="C9" s="57"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="33"/>
+      <c r="C9" s="78"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="84"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="25"/>
       <c r="L9" s="5"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
@@ -1417,18 +1435,18 @@
     </row>
     <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="60"/>
-      <c r="J10" s="60"/>
-      <c r="K10" s="49"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="75"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="35"/>
       <c r="L10" s="5"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
@@ -1448,20 +1466,20 @@
     </row>
     <row r="11" spans="1:27" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="61" t="s">
-        <v>42</v>
+      <c r="B11" s="97" t="s">
+        <v>40</v>
       </c>
-      <c r="C11" s="57"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="60" t="s">
+      <c r="C11" s="78"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="84"/>
+      <c r="H11" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="60"/>
-      <c r="J11" s="60"/>
-      <c r="K11" s="49"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="35"/>
       <c r="L11" s="5"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
@@ -1481,20 +1499,20 @@
     </row>
     <row r="12" spans="1:27" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="61" t="s">
-        <v>43</v>
+      <c r="B12" s="97" t="s">
+        <v>41</v>
       </c>
-      <c r="C12" s="57"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="62" t="s">
+      <c r="C12" s="78"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="I12" s="62"/>
-      <c r="J12" s="62"/>
-      <c r="K12" s="63" t="s">
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="39" t="s">
         <v>10</v>
       </c>
       <c r="L12" s="5"/>
@@ -1516,20 +1534,20 @@
     </row>
     <row r="13" spans="1:27" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
-      <c r="B13" s="56" t="s">
+      <c r="B13" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="57"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="39" t="s">
+      <c r="C13" s="78"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="64" t="s">
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="40" t="s">
         <v>10</v>
       </c>
       <c r="L13" s="5"/>
@@ -1551,22 +1569,22 @@
     </row>
     <row r="14" spans="1:27" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="31" t="s">
-        <v>44</v>
+      <c r="B14" s="23" t="s">
+        <v>42</v>
       </c>
-      <c r="C14" s="39"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="62" t="s">
+      <c r="C14" s="28"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="76"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="66">
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="42">
         <f>J20</f>
-        <v>6720</v>
+        <v>0</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="3"/>
@@ -1587,20 +1605,20 @@
     </row>
     <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="67"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="68" t="s">
+      <c r="B15" s="98"/>
+      <c r="C15" s="78"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="I15" s="57"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="69">
+      <c r="I15" s="78"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="43">
         <f>J20</f>
-        <v>6720</v>
+        <v>0</v>
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="3"/>
@@ -1621,16 +1639,16 @@
     </row>
     <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
-      <c r="B16" s="70"/>
-      <c r="C16" s="71"/>
-      <c r="D16" s="72"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="72"/>
-      <c r="H16" s="73"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="60"/>
-      <c r="K16" s="49"/>
+      <c r="B16" s="85"/>
+      <c r="C16" s="86"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="85"/>
+      <c r="F16" s="86"/>
+      <c r="G16" s="87"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="37"/>
+      <c r="K16" s="35"/>
       <c r="L16" s="5"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
@@ -1650,92 +1668,68 @@
     </row>
     <row r="17" spans="1:27" ht="81" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
-      <c r="B17" s="74" t="s">
+      <c r="B17" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="75" t="s">
+      <c r="C17" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="76" t="s">
+      <c r="D17" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="E17" s="77" t="s">
+      <c r="E17" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="F17" s="75" t="s">
-        <v>40</v>
+      <c r="F17" s="46" t="s">
+        <v>38</v>
       </c>
-      <c r="G17" s="76" t="s">
+      <c r="G17" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="H17" s="75" t="s">
+      <c r="H17" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="I17" s="75" t="s">
+      <c r="I17" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="J17" s="75" t="s">
+      <c r="J17" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="K17" s="78" t="s">
+      <c r="K17" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="L17" s="21" t="s">
+      <c r="L17" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="11"/>
-      <c r="W17" s="11"/>
-      <c r="X17" s="11"/>
-      <c r="Y17" s="11"/>
-      <c r="Z17" s="11"/>
-      <c r="AA17" s="11"/>
-    </row>
-    <row r="18" spans="1:27" ht="59.25" x14ac:dyDescent="0.3">
-      <c r="A18" s="12"/>
-      <c r="B18" s="79" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="80">
-        <v>45996</v>
-      </c>
-      <c r="D18" s="81">
-        <v>744</v>
-      </c>
-      <c r="E18" s="81">
-        <v>27536</v>
-      </c>
-      <c r="F18" s="82">
-        <v>6700231417</v>
-      </c>
-      <c r="G18" s="81">
-        <v>291</v>
-      </c>
-      <c r="H18" s="83">
-        <v>3000</v>
-      </c>
-      <c r="I18" s="84">
-        <f t="shared" ref="I18:I19" si="0">H18*0.12</f>
-        <v>360</v>
-      </c>
-      <c r="J18" s="84">
-        <f t="shared" ref="J18:J19" si="1">H18+I18</f>
-        <v>3360</v>
-      </c>
-      <c r="K18" s="85" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" s="104" t="s">
-        <v>45</v>
-      </c>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="10"/>
+      <c r="V17" s="10"/>
+      <c r="W17" s="10"/>
+      <c r="X17" s="10"/>
+      <c r="Y17" s="10"/>
+      <c r="Z17" s="10"/>
+      <c r="AA17" s="10"/>
+    </row>
+    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="50"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="55"/>
+      <c r="J18" s="55"/>
+      <c r="K18" s="56"/>
+      <c r="L18" s="65"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
@@ -1752,43 +1746,19 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
     </row>
-    <row r="19" spans="1:27" ht="59.25" x14ac:dyDescent="0.3">
-      <c r="A19" s="12"/>
-      <c r="B19" s="79" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="86">
-        <v>45996</v>
-      </c>
-      <c r="D19" s="81">
-        <v>745</v>
-      </c>
-      <c r="E19" s="81">
-        <v>27532</v>
-      </c>
-      <c r="F19" s="82">
-        <v>6700231417</v>
-      </c>
-      <c r="G19" s="81">
-        <v>285</v>
-      </c>
-      <c r="H19" s="83">
-        <v>3000</v>
-      </c>
-      <c r="I19" s="84">
-        <f t="shared" si="0"/>
-        <v>360</v>
-      </c>
-      <c r="J19" s="84">
-        <f t="shared" si="1"/>
-        <v>3360</v>
-      </c>
-      <c r="K19" s="85" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" s="104" t="s">
-        <v>46</v>
-      </c>
+    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A19" s="11"/>
+      <c r="B19" s="50"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="56"/>
+      <c r="L19" s="65"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
@@ -1806,29 +1776,29 @@
       <c r="AA19" s="3"/>
     </row>
     <row r="20" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="14"/>
-      <c r="B20" s="87" t="s">
-        <v>27</v>
+      <c r="A20" s="13"/>
+      <c r="B20" s="58" t="s">
+        <v>25</v>
       </c>
-      <c r="C20" s="88"/>
-      <c r="D20" s="88"/>
-      <c r="E20" s="88"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="89">
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="60">
         <f>SUM(H18:H19)</f>
-        <v>6000</v>
+        <v>0</v>
       </c>
-      <c r="I20" s="89">
+      <c r="I20" s="60">
         <f>SUM(I18:I19)</f>
-        <v>720</v>
+        <v>0</v>
       </c>
-      <c r="J20" s="89">
+      <c r="J20" s="60">
         <f>SUM(J18:J19)</f>
-        <v>6720</v>
+        <v>0</v>
       </c>
-      <c r="K20" s="89"/>
-      <c r="L20" s="19"/>
+      <c r="K20" s="60"/>
+      <c r="L20" s="18"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
@@ -1847,16 +1817,16 @@
     </row>
     <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="39"/>
-      <c r="K21" s="39"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
       <c r="L21" s="5"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
@@ -1876,16 +1846,16 @@
     </row>
     <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
       <c r="L22" s="5"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
@@ -1903,26 +1873,26 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="15"/>
-      <c r="B23" s="90"/>
-      <c r="C23" s="91" t="s">
+    <row r="23" spans="1:27" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="14"/>
+      <c r="B23" s="61"/>
+      <c r="C23" s="99" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="99"/>
+      <c r="E23" s="100" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="72"/>
+      <c r="G23" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="91"/>
-      <c r="E23" s="92" t="s">
+      <c r="H23" s="72"/>
+      <c r="I23" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="F23" s="30"/>
-      <c r="G23" s="93" t="s">
-        <v>30</v>
-      </c>
-      <c r="H23" s="30"/>
-      <c r="I23" s="93" t="s">
-        <v>31</v>
-      </c>
-      <c r="J23" s="29"/>
-      <c r="K23" s="30"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="72"/>
       <c r="L23" s="5"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
@@ -1941,25 +1911,25 @@
       <c r="AA23" s="3"/>
     </row>
     <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="16"/>
-      <c r="B24" s="94"/>
-      <c r="C24" s="95" t="s">
+      <c r="A24" s="15"/>
+      <c r="B24" s="62"/>
+      <c r="C24" s="101" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="101"/>
+      <c r="E24" s="102" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="103"/>
+      <c r="G24" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="95"/>
-      <c r="E24" s="96" t="s">
+      <c r="H24" s="75"/>
+      <c r="I24" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="97"/>
-      <c r="G24" s="98" t="s">
-        <v>34</v>
-      </c>
-      <c r="H24" s="58"/>
-      <c r="I24" s="98" t="s">
-        <v>35</v>
-      </c>
-      <c r="J24" s="57"/>
-      <c r="K24" s="58"/>
+      <c r="J24" s="78"/>
+      <c r="K24" s="75"/>
       <c r="L24" s="5"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
@@ -1978,17 +1948,17 @@
       <c r="AA24" s="3"/>
     </row>
     <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="16"/>
-      <c r="B25" s="99"/>
-      <c r="C25" s="95"/>
-      <c r="D25" s="95"/>
-      <c r="E25" s="100"/>
-      <c r="F25" s="101"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="34"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="58"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="63"/>
+      <c r="C25" s="101"/>
+      <c r="D25" s="101"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="76"/>
+      <c r="J25" s="78"/>
+      <c r="K25" s="75"/>
       <c r="L25" s="5"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
@@ -2007,25 +1977,25 @@
       <c r="AA25" s="3"/>
     </row>
     <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="102"/>
-      <c r="C26" s="103" t="s">
+      <c r="A26" s="16"/>
+      <c r="B26" s="64"/>
+      <c r="C26" s="106" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="106"/>
+      <c r="E26" s="100" t="s">
+        <v>35</v>
+      </c>
+      <c r="F26" s="72"/>
+      <c r="G26" s="77" t="s">
         <v>36</v>
       </c>
-      <c r="D26" s="103"/>
-      <c r="E26" s="92" t="s">
+      <c r="H26" s="72"/>
+      <c r="I26" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="F26" s="30"/>
-      <c r="G26" s="93" t="s">
-        <v>38</v>
-      </c>
-      <c r="H26" s="30"/>
-      <c r="I26" s="93" t="s">
-        <v>39</v>
-      </c>
-      <c r="J26" s="29"/>
-      <c r="K26" s="30"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="72"/>
       <c r="L26" s="5"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
@@ -2193,8 +2163,8 @@
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -2221,12 +2191,12 @@
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+      <c r="D33" s="66"/>
+      <c r="E33" s="67"/>
+      <c r="F33" s="67"/>
+      <c r="G33" s="66"/>
+      <c r="H33" s="66"/>
+      <c r="I33" s="66"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
@@ -2250,12 +2220,12 @@
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="67"/>
+      <c r="F34" s="67"/>
+      <c r="G34" s="66"/>
+      <c r="H34" s="66"/>
+      <c r="I34" s="66"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
@@ -2279,12 +2249,12 @@
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+      <c r="D35" s="66"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="66"/>
+      <c r="G35" s="66"/>
+      <c r="H35" s="66"/>
+      <c r="I35" s="66"/>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
@@ -2308,12 +2278,12 @@
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
+      <c r="D36" s="66"/>
+      <c r="E36" s="66"/>
+      <c r="F36" s="66"/>
+      <c r="G36" s="66"/>
+      <c r="H36" s="66"/>
+      <c r="I36" s="66"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
@@ -2337,12 +2307,12 @@
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
+      <c r="D37" s="66"/>
+      <c r="E37" s="66"/>
+      <c r="F37" s="66"/>
+      <c r="G37" s="66"/>
+      <c r="H37" s="66"/>
+      <c r="I37" s="66"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
@@ -2366,12 +2336,12 @@
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="20"/>
+      <c r="D38" s="66"/>
+      <c r="E38" s="66"/>
+      <c r="F38" s="66"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="66"/>
+      <c r="I38" s="69"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
@@ -2395,12 +2365,12 @@
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="18"/>
+      <c r="D39" s="66"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="66"/>
+      <c r="G39" s="66"/>
+      <c r="H39" s="66"/>
+      <c r="I39" s="67"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
@@ -2429,7 +2399,7 @@
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
-      <c r="I40" s="18"/>
+      <c r="I40" s="17"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
@@ -2458,7 +2428,7 @@
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
-      <c r="I41" s="18"/>
+      <c r="I41" s="17"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
@@ -2487,7 +2457,7 @@
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
-      <c r="I42" s="18"/>
+      <c r="I42" s="17"/>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
@@ -2516,7 +2486,7 @@
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
-      <c r="I43" s="18"/>
+      <c r="I43" s="17"/>
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
@@ -2545,7 +2515,7 @@
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
-      <c r="I44" s="18"/>
+      <c r="I44" s="17"/>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
@@ -2574,7 +2544,7 @@
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
-      <c r="I45" s="18"/>
+      <c r="I45" s="17"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
@@ -2603,7 +2573,7 @@
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
-      <c r="I46" s="18"/>
+      <c r="I46" s="17"/>
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
@@ -2632,7 +2602,7 @@
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
-      <c r="I47" s="18"/>
+      <c r="I47" s="17"/>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
@@ -2661,7 +2631,7 @@
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
-      <c r="I48" s="18"/>
+      <c r="I48" s="17"/>
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
@@ -2690,7 +2660,7 @@
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
-      <c r="I49" s="18"/>
+      <c r="I49" s="17"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
@@ -2719,7 +2689,7 @@
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
-      <c r="I50" s="18"/>
+      <c r="I50" s="17"/>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
@@ -2748,7 +2718,7 @@
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
-      <c r="I51" s="18"/>
+      <c r="I51" s="17"/>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
@@ -2777,7 +2747,7 @@
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
-      <c r="I52" s="18"/>
+      <c r="I52" s="17"/>
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
@@ -2806,7 +2776,7 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
-      <c r="I53" s="18"/>
+      <c r="I53" s="17"/>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
@@ -2835,7 +2805,7 @@
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
-      <c r="I54" s="18"/>
+      <c r="I54" s="17"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
@@ -2864,7 +2834,7 @@
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
-      <c r="I55" s="18"/>
+      <c r="I55" s="17"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
@@ -29944,7 +29914,7 @@
     <row r="989" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A989" s="3"/>
       <c r="B989" s="3"/>
-      <c r="C989" s="13">
+      <c r="C989" s="12">
         <v>45911</v>
       </c>
       <c r="D989" s="3"/>
@@ -29973,12 +29943,6 @@
       <c r="AA989" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="B17:L20" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState ref="B18:L20">
-      <sortCondition ref="C17:C20"/>
-      <sortCondition ref="D17:D20"/>
-    </sortState>
-  </autoFilter>
   <mergeCells count="27">
     <mergeCell ref="I26:K26"/>
     <mergeCell ref="G26:H26"/>
